--- a/Backend/Dashboard/src/main/resources/templates/Project_Template 2.xlsx
+++ b/Backend/Dashboard/src/main/resources/templates/Project_Template 2.xlsx
@@ -9,19 +9,19 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet4" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Project schedule" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="FinWiz_Project_Schedule" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Sheet1" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Titles" vbProcedure="false">'Project schedule'!$5:$7</definedName>
-    <definedName function="false" hidden="false" name="Actual_End" vbProcedure="false">'Project schedule'!$L$8</definedName>
-    <definedName function="false" hidden="false" name="Display_Week" vbProcedure="false">'Project schedule'!$AA$3</definedName>
-    <definedName function="false" hidden="false" name="Planned_End" vbProcedure="false">'Project schedule'!$J$8</definedName>
-    <definedName function="false" hidden="false" name="Progress" vbProcedure="false">'Project schedule'!$N$8</definedName>
-    <definedName function="false" hidden="false" name="Project_Start" vbProcedure="false">'Project schedule'!$AA$2</definedName>
-    <definedName function="false" hidden="false" localSheetId="1" name="task_end" vbProcedure="false">'Project schedule'!$L1</definedName>
-    <definedName function="false" hidden="false" localSheetId="1" name="task_progress" vbProcedure="false">'Project schedule'!$E1</definedName>
-    <definedName function="false" hidden="false" localSheetId="1" name="task_start" vbProcedure="false">'Project schedule'!$K1</definedName>
+    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Titles" vbProcedure="false">FinWiz_Project_Schedule!$5:$7</definedName>
+    <definedName function="false" hidden="false" name="Actual_End" vbProcedure="false">FinWiz_Project_Schedule!$L$8</definedName>
+    <definedName function="false" hidden="false" name="Display_Week" vbProcedure="false">FinWiz_Project_Schedule!$AA$3</definedName>
+    <definedName function="false" hidden="false" name="Planned_End" vbProcedure="false">FinWiz_Project_Schedule!$J$8</definedName>
+    <definedName function="false" hidden="false" name="Progress" vbProcedure="false">FinWiz_Project_Schedule!$N$8</definedName>
+    <definedName function="false" hidden="false" name="Project_Start" vbProcedure="false">FinWiz_Project_Schedule!$AA$2</definedName>
+    <definedName function="false" hidden="false" localSheetId="1" name="task_end" vbProcedure="false">FinWiz_Project_Schedule!$L1</definedName>
+    <definedName function="false" hidden="false" localSheetId="1" name="task_progress" vbProcedure="false">FinWiz_Project_Schedule!$E1</definedName>
+    <definedName function="false" hidden="false" localSheetId="1" name="task_start" vbProcedure="false">FinWiz_Project_Schedule!$K1</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="today" vbProcedure="false">TODAY()</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -963,7 +963,7 @@
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" recordCount="3" createdVersion="3">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A5:O105" sheet="Project schedule"/>
+    <worksheetSource ref="A5:O105" sheet="FinWiz_Project_Schedule"/>
   </cacheSource>
   <cacheFields count="15">
     <cacheField name="Sr. No." numFmtId="0">
@@ -4824,7 +4824,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2F43C310-1D7C-4C17-99A0-1FA1FB8066B7}</x14:id>
+          <x14:id>{80CF959D-DCF7-4BA2-8197-C3B88D7491BD}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4842,7 +4842,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2F43C310-1D7C-4C17-99A0-1FA1FB8066B7}">
+          <x14:cfRule type="dataBar" id="{80CF959D-DCF7-4BA2-8197-C3B88D7491BD}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="automatic" gradient="true">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
